--- a/tools/size-charts/size-chart.xlsx
+++ b/tools/size-charts/size-chart.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Samiksha Data Backup\SAMIKSHA\SHOPIFY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="40">
   <si>
     <t>Article</t>
   </si>
@@ -144,22 +144,17 @@
   </si>
   <si>
     <t>Sweatshirts</t>
+  </si>
+  <si>
+    <t>Plus Size Shirts</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -187,7 +182,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -247,55 +242,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -308,14 +265,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="12" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -327,24 +284,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -625,500 +571,463 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.85546875" customWidth="1"/>
-    <col min="5" max="5" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
+    <col min="2" max="2" width="16.88671875" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3">
-        <v>38</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="D2" s="2">
         <v>16.5</v>
       </c>
-      <c r="F2" s="3">
+      <c r="E2" s="2">
         <v>41.5</v>
       </c>
-      <c r="G2" s="3">
+      <c r="F2" s="2">
         <v>29.25</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3">
-        <v>40</v>
-      </c>
-      <c r="E3" s="3">
+      <c r="D3" s="2">
         <v>17.25</v>
       </c>
-      <c r="F3" s="3">
+      <c r="E3" s="2">
         <v>43.5</v>
       </c>
-      <c r="G3" s="3">
+      <c r="F3" s="2">
         <v>29.75</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="3" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3">
-        <v>42</v>
-      </c>
-      <c r="E4" s="3">
+      <c r="D4" s="2">
         <v>18</v>
       </c>
-      <c r="F4" s="3">
+      <c r="E4" s="2">
         <v>46</v>
       </c>
-      <c r="G4" s="3">
+      <c r="F4" s="2">
         <v>30.25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="3" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3">
-        <v>44</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D5" s="2">
         <v>18.75</v>
       </c>
-      <c r="F5" s="3">
+      <c r="E5" s="2">
         <v>48</v>
       </c>
-      <c r="G5" s="3">
+      <c r="F5" s="2">
         <v>30.75</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="3" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
+        <v>19.5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>50</v>
+      </c>
+      <c r="F6" s="2">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="15"/>
+      <c r="B7" s="15"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="2">
+        <v>20.5</v>
+      </c>
+      <c r="E9" s="2">
+        <v>53</v>
+      </c>
+      <c r="F9" s="2">
+        <v>33.625</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="2">
+        <v>21.25</v>
+      </c>
+      <c r="E10" s="2">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="2">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2">
+        <v>57.5</v>
+      </c>
+      <c r="F11" s="2">
+        <v>34.375</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="2">
+        <v>22.75</v>
+      </c>
+      <c r="E12" s="2">
+        <v>60</v>
+      </c>
+      <c r="F12" s="2">
+        <v>34.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="E15" s="2">
+        <v>44.5</v>
+      </c>
+      <c r="F15" s="2">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="2">
+        <v>19.125</v>
+      </c>
+      <c r="E16" s="2">
         <v>46</v>
       </c>
-      <c r="E6" s="3">
-        <v>19.5</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="F16" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2">
+        <v>19.75</v>
+      </c>
+      <c r="E17" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="F17" s="2">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2">
+        <v>20.375</v>
+      </c>
+      <c r="E18" s="2">
+        <v>49</v>
+      </c>
+      <c r="F18" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2">
+        <v>21</v>
+      </c>
+      <c r="E19" s="2">
+        <v>50.5</v>
+      </c>
+      <c r="F19" s="2">
+        <v>31.5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" s="2">
+        <v>16.25</v>
+      </c>
+      <c r="E22" s="2">
+        <v>39</v>
+      </c>
+      <c r="F22" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D23" s="2">
+        <v>17</v>
+      </c>
+      <c r="E23" s="2">
+        <v>41</v>
+      </c>
+      <c r="F23" s="2">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2">
+        <v>17.75</v>
+      </c>
+      <c r="E24" s="2">
+        <v>43</v>
+      </c>
+      <c r="F24" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="E25" s="2">
+        <v>45</v>
+      </c>
+      <c r="F25" s="2">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2">
+        <v>19.25</v>
+      </c>
+      <c r="E26" s="2">
+        <v>47.5</v>
+      </c>
+      <c r="F26" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="2">
+        <v>20</v>
+      </c>
+      <c r="E27" s="2">
         <v>50</v>
       </c>
-      <c r="G6" s="3">
-        <v>31.25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="3">
-        <v>48</v>
-      </c>
-      <c r="E7" s="3">
-        <v>20.5</v>
-      </c>
-      <c r="F7" s="3">
-        <v>53</v>
-      </c>
-      <c r="G7" s="3">
-        <v>33.625</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="3" t="s">
+      <c r="F27" s="2">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="3">
-        <v>50</v>
-      </c>
-      <c r="E8" s="3">
-        <v>21.25</v>
-      </c>
-      <c r="F8" s="3">
-        <v>55</v>
-      </c>
-      <c r="G8" s="3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="3">
-        <v>52</v>
-      </c>
-      <c r="E9" s="3">
-        <v>22</v>
-      </c>
-      <c r="F9" s="3">
-        <v>57.5</v>
-      </c>
-      <c r="G9" s="3">
-        <v>34.375</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="12"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D10" s="3">
-        <v>54</v>
-      </c>
-      <c r="E10" s="3">
-        <v>22.75</v>
-      </c>
-      <c r="F10" s="3">
-        <v>60</v>
-      </c>
-      <c r="G10" s="3">
-        <v>34.75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="3">
-        <v>38</v>
-      </c>
-      <c r="E13" s="3">
-        <v>18.5</v>
-      </c>
-      <c r="F13" s="3">
-        <v>44.5</v>
-      </c>
-      <c r="G13" s="3">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="3">
-        <v>40</v>
-      </c>
-      <c r="E14" s="3">
-        <v>19.125</v>
-      </c>
-      <c r="F14" s="3">
-        <v>46</v>
-      </c>
-      <c r="G14" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15" s="3">
-        <v>42</v>
-      </c>
-      <c r="E15" s="3">
-        <v>19.75</v>
-      </c>
-      <c r="F15" s="3">
-        <v>47.5</v>
-      </c>
-      <c r="G15" s="3">
-        <v>30.5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="3">
-        <v>44</v>
-      </c>
-      <c r="E16" s="3">
-        <v>20.375</v>
-      </c>
-      <c r="F16" s="3">
-        <v>49</v>
-      </c>
-      <c r="G16" s="3">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="12"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D17" s="3">
-        <v>46</v>
-      </c>
-      <c r="E17" s="3">
-        <v>21</v>
-      </c>
-      <c r="F17" s="3">
-        <v>50.5</v>
-      </c>
-      <c r="G17" s="3">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D20" s="3">
-        <v>38</v>
-      </c>
-      <c r="E20" s="3">
-        <v>16.25</v>
-      </c>
-      <c r="F20" s="3">
-        <v>39</v>
-      </c>
-      <c r="G20" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="12"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="3">
-        <v>40</v>
-      </c>
-      <c r="E21" s="3">
-        <v>17</v>
-      </c>
-      <c r="F21" s="3">
-        <v>41</v>
-      </c>
-      <c r="G21" s="3">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="3">
-        <v>42</v>
-      </c>
-      <c r="E22" s="3">
-        <v>17.75</v>
-      </c>
-      <c r="F22" s="3">
-        <v>43</v>
-      </c>
-      <c r="G22" s="3">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="12"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="3">
-        <v>44</v>
-      </c>
-      <c r="E23" s="3">
-        <v>18.5</v>
-      </c>
-      <c r="F23" s="3">
-        <v>45</v>
-      </c>
-      <c r="G23" s="3">
-        <v>28.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="12"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="3">
-        <v>46</v>
-      </c>
-      <c r="E24" s="3">
-        <v>19.25</v>
-      </c>
-      <c r="F24" s="3">
-        <v>47.5</v>
-      </c>
-      <c r="G24" s="3">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="12"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="3">
-        <v>48</v>
-      </c>
-      <c r="E25" s="3">
-        <v>20</v>
-      </c>
-      <c r="F25" s="3">
-        <v>50</v>
-      </c>
-      <c r="G25" s="3">
-        <v>29.5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="12"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="3">
-        <v>50</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D28" s="2">
         <v>20.75</v>
       </c>
-      <c r="F26" s="3">
+      <c r="E28" s="2">
         <v>52.5</v>
       </c>
-      <c r="G26" s="3">
+      <c r="F28" s="2">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A2:A10"/>
-    <mergeCell ref="B2:B10"/>
-    <mergeCell ref="A13:A17"/>
-    <mergeCell ref="B13:B17"/>
-    <mergeCell ref="A20:A26"/>
-    <mergeCell ref="B20:B26"/>
+  <mergeCells count="8">
+    <mergeCell ref="A15:A19"/>
+    <mergeCell ref="B15:B19"/>
+    <mergeCell ref="A22:A28"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="B9:B12"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1127,805 +1036,805 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="15"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="C1" s="12"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="14"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>28</v>
       </c>
-      <c r="C2" s="6">
-        <v>30</v>
-      </c>
-      <c r="D2" s="6">
+      <c r="C2" s="5">
+        <v>30</v>
+      </c>
+      <c r="D2" s="5">
         <v>32</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>34</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>36</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G2" s="5">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="6">
         <v>29.5</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3" s="6">
         <v>31.5</v>
       </c>
-      <c r="D3" s="7">
+      <c r="D3" s="6">
         <v>33.5</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>35.5</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>37.5</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="6">
         <v>39.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="6">
         <v>38.5</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="6">
         <v>40.5</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="6">
         <v>42.5</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>44.5</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>46.5</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="6">
         <v>48.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="5">
         <v>19</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="6">
         <v>19.5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <v>20</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>20.5</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>21</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="6">
         <v>21.5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="6">
-        <v>30</v>
-      </c>
-      <c r="C6" s="6">
-        <v>30</v>
-      </c>
-      <c r="D6" s="6">
-        <v>30</v>
-      </c>
-      <c r="E6" s="6">
-        <v>30</v>
-      </c>
-      <c r="F6" s="6">
-        <v>30</v>
-      </c>
-      <c r="G6" s="6">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
+      <c r="B6" s="5">
+        <v>30</v>
+      </c>
+      <c r="C6" s="5">
+        <v>30</v>
+      </c>
+      <c r="D6" s="5">
+        <v>30</v>
+      </c>
+      <c r="E6" s="5">
+        <v>30</v>
+      </c>
+      <c r="F6" s="5">
+        <v>30</v>
+      </c>
+      <c r="G6" s="5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="15"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="B8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="14"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="5">
         <v>28</v>
       </c>
-      <c r="C9" s="6">
-        <v>30</v>
-      </c>
-      <c r="D9" s="6">
+      <c r="C9" s="5">
+        <v>30</v>
+      </c>
+      <c r="D9" s="5">
         <v>32</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>34</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>36</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="5">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="5">
         <v>29</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <v>31</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <v>33</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>35</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>37</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="5">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="6">
         <v>36.5</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="6">
         <v>38.5</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="6">
         <v>40.5</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>42.5</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <v>44.5</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11" s="6">
         <v>46.5</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="6">
         <v>12</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <v>12.5</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="6">
         <v>13</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="5">
         <v>13.5</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <v>14</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="5">
         <v>14.5</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="5">
         <v>31</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="5">
         <v>31</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="5">
         <v>31</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>31</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="5">
         <v>31</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="5">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="6"/>
-      <c r="E14" s="6"/>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="C15" s="12"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16" s="5">
         <v>28</v>
       </c>
-      <c r="C16" s="6">
-        <v>30</v>
-      </c>
-      <c r="D16" s="6">
+      <c r="C16" s="5">
+        <v>30</v>
+      </c>
+      <c r="D16" s="5">
         <v>32</v>
       </c>
-      <c r="E16" s="6">
+      <c r="E16" s="5">
         <v>34</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="5">
         <v>36</v>
       </c>
-      <c r="G16" s="6">
+      <c r="G16" s="5">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="6">
         <v>29.5</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="6">
         <v>31.5</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="6">
         <v>33.5</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6">
         <v>35.5</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <v>37.5</v>
       </c>
-      <c r="G17" s="7">
+      <c r="G17" s="6">
         <v>39.5</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="6">
         <v>36.5</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="6">
         <v>38.5</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="6">
         <v>40.5</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>42.5</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <v>44.5</v>
       </c>
-      <c r="G18" s="7">
+      <c r="G18" s="6">
         <v>46.5</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="5">
         <v>11.5</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="6">
         <v>12</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <v>12.5</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>13</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="5">
         <v>13.5</v>
       </c>
-      <c r="G19" s="7">
+      <c r="G19" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="5">
         <v>29</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <v>29</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <v>29</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>29</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="5">
         <v>29</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="5">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
-      <c r="C21" s="6"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
+      <c r="C22" s="12"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="6">
+      <c r="B23" s="5">
         <v>28</v>
       </c>
-      <c r="C23" s="6">
-        <v>30</v>
-      </c>
-      <c r="D23" s="6">
+      <c r="C23" s="5">
+        <v>30</v>
+      </c>
+      <c r="D23" s="5">
         <v>32</v>
       </c>
-      <c r="E23" s="6">
+      <c r="E23" s="5">
         <v>34</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="5">
         <v>36</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G23" s="5">
         <v>38</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="8">
-        <v>30</v>
-      </c>
-      <c r="C24" s="7">
+      <c r="B24" s="7">
+        <v>30</v>
+      </c>
+      <c r="C24" s="6">
         <v>32</v>
       </c>
-      <c r="D24" s="7">
+      <c r="D24" s="6">
         <v>34</v>
       </c>
-      <c r="E24" s="7">
+      <c r="E24" s="6">
         <v>36</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <v>38</v>
       </c>
-      <c r="G24" s="7">
+      <c r="G24" s="6">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="6">
+      <c r="B25" s="5">
         <v>37</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <v>39</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <v>41</v>
       </c>
-      <c r="E25" s="6">
+      <c r="E25" s="5">
         <v>43</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="5">
         <v>45</v>
       </c>
-      <c r="G25" s="6">
+      <c r="G25" s="5">
         <v>47</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="6">
         <v>14.5</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <v>15</v>
       </c>
-      <c r="D26" s="7">
+      <c r="D26" s="6">
         <v>15.5</v>
       </c>
-      <c r="E26" s="6">
+      <c r="E26" s="5">
         <v>16</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <v>16.5</v>
       </c>
-      <c r="G26" s="6">
+      <c r="G26" s="5">
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="6">
+      <c r="B27" s="5">
         <v>31</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <v>31</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <v>31</v>
       </c>
-      <c r="E27" s="6">
+      <c r="E27" s="5">
         <v>31</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="5">
         <v>31</v>
       </c>
-      <c r="G27" s="6">
+      <c r="G27" s="5">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="15"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="C28" s="12"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="14"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="6">
+      <c r="B29" s="5">
         <v>28</v>
       </c>
-      <c r="C29" s="6">
-        <v>30</v>
-      </c>
-      <c r="D29" s="6">
+      <c r="C29" s="5">
+        <v>30</v>
+      </c>
+      <c r="D29" s="5">
         <v>32</v>
       </c>
-      <c r="E29" s="6">
+      <c r="E29" s="5">
         <v>34</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="5">
         <v>36</v>
       </c>
-      <c r="G29" s="6">
+      <c r="G29" s="5">
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="6">
         <v>29.75</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="6">
         <v>31.75</v>
       </c>
-      <c r="D30" s="7">
+      <c r="D30" s="6">
         <v>33.75</v>
       </c>
-      <c r="E30" s="7">
+      <c r="E30" s="6">
         <v>35.75</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <v>37.75</v>
       </c>
-      <c r="G30" s="7">
+      <c r="G30" s="6">
         <v>39.75</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B31" s="6">
+      <c r="B31" s="5">
         <v>38</v>
       </c>
-      <c r="C31" s="6">
+      <c r="C31" s="5">
         <v>40</v>
       </c>
-      <c r="D31" s="6">
+      <c r="D31" s="5">
         <v>42</v>
       </c>
-      <c r="E31" s="6">
+      <c r="E31" s="5">
         <v>44</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="5">
         <v>46</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="5">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="6">
         <v>23</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="6">
         <v>23.5</v>
       </c>
-      <c r="D32" s="7">
+      <c r="D32" s="6">
         <v>24</v>
       </c>
-      <c r="E32" s="7">
+      <c r="E32" s="6">
         <v>24.5</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <v>25</v>
       </c>
-      <c r="G32" s="7">
+      <c r="G32" s="6">
         <v>25.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B33" s="6">
+      <c r="B33" s="5">
         <v>28</v>
       </c>
-      <c r="C33" s="6">
+      <c r="C33" s="5">
         <v>28</v>
       </c>
-      <c r="D33" s="6">
+      <c r="D33" s="5">
         <v>28</v>
       </c>
-      <c r="E33" s="6">
+      <c r="E33" s="5">
         <v>28</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="5">
         <v>28</v>
       </c>
-      <c r="G33" s="6">
+      <c r="G33" s="5">
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C34" s="13"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="15"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
+      <c r="C34" s="12"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="14"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B35" s="6">
+      <c r="B35" s="5">
         <v>28</v>
       </c>
-      <c r="C35" s="6">
-        <v>30</v>
-      </c>
-      <c r="D35" s="6">
+      <c r="C35" s="5">
+        <v>30</v>
+      </c>
+      <c r="D35" s="5">
         <v>32</v>
       </c>
-      <c r="E35" s="6">
+      <c r="E35" s="5">
         <v>34</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="5">
         <v>36</v>
       </c>
-      <c r="G35" s="6">
+      <c r="G35" s="5">
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B36" s="6">
+      <c r="B36" s="5">
         <v>29</v>
       </c>
-      <c r="C36" s="6">
+      <c r="C36" s="5">
         <v>31</v>
       </c>
-      <c r="D36" s="6">
+      <c r="D36" s="5">
         <v>33</v>
       </c>
-      <c r="E36" s="6">
+      <c r="E36" s="5">
         <v>35</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="5">
         <v>37</v>
       </c>
-      <c r="G36" s="6">
+      <c r="G36" s="5">
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="6">
         <v>36.5</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="6">
         <v>38.5</v>
       </c>
-      <c r="D37" s="7">
+      <c r="D37" s="6">
         <v>40.5</v>
       </c>
-      <c r="E37" s="7">
+      <c r="E37" s="6">
         <v>42.5</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="6">
         <v>44.5</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37" s="6">
         <v>46.5</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="6">
         <v>12</v>
       </c>
-      <c r="C38" s="6">
+      <c r="C38" s="5">
         <v>12.5</v>
       </c>
-      <c r="D38" s="7">
+      <c r="D38" s="6">
         <v>13</v>
       </c>
-      <c r="E38" s="6">
+      <c r="E38" s="5">
         <v>13.5</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="6">
         <v>14</v>
       </c>
-      <c r="G38" s="6">
+      <c r="G38" s="5">
         <v>14.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B39" s="6">
+      <c r="B39" s="5">
         <v>31</v>
       </c>
-      <c r="C39" s="6">
+      <c r="C39" s="5">
         <v>31</v>
       </c>
-      <c r="D39" s="6">
+      <c r="D39" s="5">
         <v>31</v>
       </c>
-      <c r="E39" s="6">
+      <c r="E39" s="5">
         <v>31</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="5">
         <v>31</v>
       </c>
-      <c r="G39" s="6">
+      <c r="G39" s="5">
         <v>31</v>
       </c>
     </row>
@@ -1945,229 +1854,229 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" customWidth="1"/>
+    <col min="4" max="4" width="28.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="2">
-        <v>30</v>
-      </c>
-      <c r="D2" s="3">
+      <c r="C2" s="1">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2">
         <v>28</v>
       </c>
-      <c r="E2" s="3">
-        <v>30</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="E2" s="2">
+        <v>30</v>
+      </c>
+      <c r="F2" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="1">
         <v>32</v>
       </c>
-      <c r="D3" s="3">
-        <v>30</v>
-      </c>
-      <c r="E3" s="3">
-        <v>30</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="D3" s="2">
+        <v>30</v>
+      </c>
+      <c r="E3" s="2">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2">
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="1">
         <v>34</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>32</v>
       </c>
-      <c r="E4" s="3">
-        <v>30</v>
-      </c>
-      <c r="F4" s="3">
+      <c r="E4" s="2">
+        <v>30</v>
+      </c>
+      <c r="F4" s="2">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="1">
         <v>36</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>34</v>
       </c>
-      <c r="E5" s="3">
-        <v>30</v>
-      </c>
-      <c r="F5" s="3">
+      <c r="E5" s="2">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="1">
         <v>38</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>36</v>
       </c>
-      <c r="E6" s="3">
-        <v>30</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="E6" s="2">
+        <v>30</v>
+      </c>
+      <c r="F6" s="2">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="1">
         <v>40</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>38</v>
       </c>
-      <c r="E7" s="3">
-        <v>30</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="E7" s="2">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="1">
         <v>40</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>42</v>
       </c>
-      <c r="E10" s="3">
-        <v>30</v>
-      </c>
-      <c r="F10" s="3">
+      <c r="E10" s="2">
+        <v>30</v>
+      </c>
+      <c r="F10" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="1">
         <v>42</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>44</v>
       </c>
-      <c r="E11" s="3">
-        <v>30</v>
-      </c>
-      <c r="F11" s="3">
+      <c r="E11" s="2">
+        <v>30</v>
+      </c>
+      <c r="F11" s="2">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="1">
         <v>44</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>46</v>
       </c>
-      <c r="E12" s="3">
-        <v>30</v>
-      </c>
-      <c r="F12" s="3">
+      <c r="E12" s="2">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="12"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="1">
         <v>46</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>48</v>
       </c>
-      <c r="E13" s="3">
-        <v>30</v>
-      </c>
-      <c r="F13" s="3">
+      <c r="E13" s="2">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2">
         <v>56</v>
       </c>
     </row>
@@ -2185,226 +2094,224 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>18.25</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>43</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>27.5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
-      <c r="C3" s="3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>18.75</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>45</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="3" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>19.5</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>48</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="12"/>
-      <c r="B5" s="12"/>
-      <c r="C5" s="3" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>20.25</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>51</v>
       </c>
-      <c r="F5" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="12"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="3" t="s">
+      <c r="F5" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>20.75</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>53</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6" s="2">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="17"/>
-      <c r="B9" s="20"/>
-      <c r="C9" s="3" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>17.5</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>42</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="2">
         <v>27.25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17"/>
-      <c r="B10" s="20"/>
-      <c r="C10" s="3" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>18.25</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>44</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="2">
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="3" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>19</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>46</v>
       </c>
-      <c r="F11" s="3">
+      <c r="F11" s="2">
         <v>29</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="3" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="3">
+      <c r="D12" s="2">
         <v>19.875</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="2">
         <v>48.5</v>
       </c>
-      <c r="F12" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18"/>
-      <c r="B13" s="21"/>
-      <c r="C13" s="3" t="s">
+      <c r="F12" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="2">
         <v>20.75</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="2">
         <v>51</v>
       </c>
-      <c r="F13" s="3">
+      <c r="F13" s="2">
         <v>31.25</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="2">
     <mergeCell ref="A2:A6"/>
     <mergeCell ref="B2:B6"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="B8:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
